--- a/design_tables/excel/EnemyAI.xlsx
+++ b/design_tables/excel/EnemyAI.xlsx
@@ -152,19 +152,6 @@
     </indexedColors>
   </colors>
 </styleSheet>
-</file>
-
-<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="EnemyAITable" displayName="EnemyAITable" ref="A1:E6" headerRowCount="1">
-  <tableColumns count="5">
-    <tableColumn id="1" name="enemy_id"/>
-    <tableColumn id="2" name="priority"/>
-    <tableColumn id="3" name="condition"/>
-    <tableColumn id="4" name="action_id"/>
-    <tableColumn id="5" name="comment"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
-</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -486,8 +473,5 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-  </tableParts>
 </worksheet>
 </file>